--- a/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,19 +56,14 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="008A8A8A"/>
+      <b val="1"/>
+      <color rgb="00B06A00"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001F7A3D"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00B06A00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -182,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,19 +210,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -254,7 +246,7 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -262,7 +254,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1272,10 +1264,14 @@
       <c r="O4" s="10" t="inlineStr"/>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>RH-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
@@ -1333,10 +1329,14 @@
       <c r="O5" s="10" t="inlineStr"/>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>RH-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1394,10 +1394,14 @@
       <c r="O6" s="10" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q6" s="10" t="inlineStr">
+        <is>
+          <t>RH-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1453,12 +1457,16 @@
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="10" t="inlineStr"/>
-      <c r="P7" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q7" s="10" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>RH-02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1516,10 +1524,14 @@
       <c r="O8" s="10" t="inlineStr"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>RH-06</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1575,12 +1587,16 @@
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q9" s="10" t="inlineStr"/>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>RH-02</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1636,12 +1652,16 @@
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="10" t="inlineStr"/>
-      <c r="P10" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr"/>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="inlineStr">
+        <is>
+          <t>RH-03</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1697,12 +1717,16 @@
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="10" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>RH-03</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1758,12 +1782,16 @@
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="10" t="inlineStr"/>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="inlineStr"/>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>RH-04</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1819,12 +1847,16 @@
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="10" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q13" s="10" t="inlineStr"/>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>RH-04</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -1880,12 +1912,16 @@
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="10" t="inlineStr"/>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q14" s="10" t="inlineStr"/>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q14" s="10" t="inlineStr">
+        <is>
+          <t>RH-04</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -1941,12 +1977,16 @@
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr"/>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>RH-05</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -2002,12 +2042,16 @@
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="10" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q16" s="10" t="inlineStr"/>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>RH-03</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -2063,12 +2107,16 @@
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="10" t="inlineStr"/>
-      <c r="P17" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q17" s="10" t="inlineStr"/>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>RH-02</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -2126,10 +2174,14 @@
       <c r="O18" s="10" t="inlineStr"/>
       <c r="P18" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q18" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>RH-07</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -2185,12 +2237,16 @@
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q19" s="10" t="inlineStr"/>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>RH-09</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -2248,10 +2304,14 @@
       <c r="O20" s="10" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q20" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q20" s="10" t="inlineStr">
+        <is>
+          <t>RH-07</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -2307,12 +2367,16 @@
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q21" s="10" t="inlineStr"/>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>RH-09</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -2368,12 +2432,16 @@
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q22" s="10" t="inlineStr"/>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>RH-08</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -2429,12 +2497,16 @@
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q23" s="10" t="inlineStr"/>
+      <c r="P23" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>RH-08</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -2490,12 +2562,16 @@
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="10" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q24" s="10" t="inlineStr"/>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>RH-08</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -2551,12 +2627,16 @@
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr"/>
+      <c r="P25" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>RH-08</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -2612,12 +2692,16 @@
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
       <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q26" s="10" t="inlineStr"/>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>RH-08</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -2675,10 +2759,14 @@
       <c r="O27" s="10" t="inlineStr"/>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q27" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>RH-10</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -2689,12 +2777,12 @@
           <t>REF-025</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2736,10 +2824,14 @@
       <c r="O28" s="10" t="inlineStr"/>
       <c r="P28" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q28" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>PL-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
@@ -2750,12 +2842,12 @@
           <t>REF-026</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2795,7 +2887,7 @@
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="13" t="inlineStr">
+      <c r="P29" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -2815,12 +2907,12 @@
           <t>REF-027</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2860,7 +2952,7 @@
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="10" t="inlineStr"/>
-      <c r="P30" s="13" t="inlineStr">
+      <c r="P30" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -2880,12 +2972,12 @@
           <t>REF-028</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Principes et interface Grasshopper</t>
         </is>
@@ -2925,7 +3017,7 @@
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" s="13" t="inlineStr">
+      <c r="P31" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -2945,12 +3037,12 @@
           <t>REF-029</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -2992,10 +3084,14 @@
       <c r="O32" s="10" t="inlineStr"/>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q32" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>PL-02</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -3006,12 +3102,12 @@
           <t>REF-030</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3053,10 +3149,14 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q33" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>PL-02</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -3067,12 +3167,12 @@
           <t>REF-031</t>
         </is>
       </c>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3112,12 +3212,16 @@
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
       <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q34" s="10" t="inlineStr"/>
+      <c r="P34" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -3128,12 +3232,12 @@
           <t>REF-032</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3173,12 +3277,16 @@
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
       <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q35" s="10" t="inlineStr"/>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -3189,12 +3297,12 @@
           <t>REF-033</t>
         </is>
       </c>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3234,12 +3342,16 @@
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="10" t="inlineStr"/>
-      <c r="P36" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q36" s="10" t="inlineStr"/>
+      <c r="P36" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -3250,12 +3362,12 @@
           <t>REF-034</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3295,12 +3407,16 @@
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="10" t="inlineStr"/>
-      <c r="P37" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="P37" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n">
@@ -3311,12 +3427,12 @@
           <t>REF-035</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3356,12 +3472,16 @@
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="10" t="inlineStr"/>
-      <c r="P38" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q38" s="10" t="inlineStr"/>
+      <c r="P38" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3372,12 +3492,12 @@
           <t>REF-036</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3417,12 +3537,16 @@
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="10" t="inlineStr"/>
-      <c r="P39" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q39" s="10" t="inlineStr"/>
+      <c r="P39" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -3433,12 +3557,12 @@
           <t>REF-037</t>
         </is>
       </c>
-      <c r="C40" s="12" t="inlineStr">
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3478,12 +3602,16 @@
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="10" t="inlineStr"/>
-      <c r="P40" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q40" s="10" t="inlineStr"/>
+      <c r="P40" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>PL-03</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -3494,12 +3622,12 @@
           <t>REF-038</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3541,10 +3669,14 @@
       <c r="O41" s="10" t="inlineStr"/>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q41" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>PL-04</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
@@ -3555,12 +3687,12 @@
           <t>REF-039</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="D42" s="12" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Écosystème de plugins</t>
         </is>
@@ -3602,10 +3734,14 @@
       <c r="O42" s="10" t="inlineStr"/>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q42" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>PL-04</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -3661,7 +3797,7 @@
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
-      <c r="P43" s="13" t="inlineStr">
+      <c r="P43" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3726,7 +3862,7 @@
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="10" t="inlineStr"/>
-      <c r="P44" s="15" t="inlineStr">
+      <c r="P44" s="11" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -3791,7 +3927,7 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="13" t="inlineStr">
+      <c r="P45" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3856,7 +3992,7 @@
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="10" t="inlineStr"/>
-      <c r="P46" s="13" t="inlineStr">
+      <c r="P46" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3921,7 +4057,7 @@
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="10" t="inlineStr"/>
-      <c r="P47" s="13" t="inlineStr">
+      <c r="P47" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3986,7 +4122,7 @@
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
       <c r="O48" s="10" t="inlineStr"/>
-      <c r="P48" s="13" t="inlineStr">
+      <c r="P48" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4051,7 +4187,7 @@
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="10" t="inlineStr"/>
-      <c r="P49" s="13" t="inlineStr">
+      <c r="P49" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4116,7 +4252,7 @@
       <c r="M50" s="7" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="10" t="inlineStr"/>
-      <c r="P50" s="13" t="inlineStr">
+      <c r="P50" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4181,7 +4317,7 @@
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="10" t="inlineStr"/>
-      <c r="P51" s="13" t="inlineStr">
+      <c r="P51" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4246,7 +4382,7 @@
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="10" t="inlineStr"/>
-      <c r="P52" s="13" t="inlineStr">
+      <c r="P52" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4311,7 +4447,7 @@
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
-      <c r="P53" s="13" t="inlineStr">
+      <c r="P53" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4376,7 +4512,7 @@
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="10" t="inlineStr"/>
-      <c r="P54" s="13" t="inlineStr">
+      <c r="P54" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4441,7 +4577,7 @@
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="10" t="inlineStr"/>
-      <c r="P55" s="13" t="inlineStr">
+      <c r="P55" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4505,12 +4641,12 @@
       <c r="L56" s="8" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="8" t="inlineStr"/>
-      <c r="O56" s="16" t="inlineStr">
+      <c r="O56" s="15" t="inlineStr">
         <is>
           <t>⚠ Vérifié dans Rhino 8 le 26/08/2026 : la correspondance PAR DÉFAUT de Grasshopper n'est pas la troncature sur la liste la plus courte, mais la correspondance sur la liste la plus LONGUE, la liste courte étant prolongée par répétition de son dernier élément. Une liste de 10 et une liste de 4 dans une Addition produisent 10 résultats, pas 4. Le mode Shortest List existe mais doit être demandé explicitement par clic droit. L'intitulé de cette notion est donc à corriger.</t>
         </is>
       </c>
-      <c r="P56" s="15" t="inlineStr">
+      <c r="P56" s="11" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -4575,7 +4711,7 @@
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
       <c r="O57" s="10" t="inlineStr"/>
-      <c r="P57" s="13" t="inlineStr">
+      <c r="P57" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4640,7 +4776,7 @@
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="10" t="inlineStr"/>
-      <c r="P58" s="13" t="inlineStr">
+      <c r="P58" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4705,7 +4841,7 @@
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="10" t="inlineStr"/>
-      <c r="P59" s="15" t="inlineStr">
+      <c r="P59" s="11" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -4770,7 +4906,7 @@
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
       <c r="O60" s="10" t="inlineStr"/>
-      <c r="P60" s="13" t="inlineStr">
+      <c r="P60" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4835,7 +4971,7 @@
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="10" t="inlineStr"/>
-      <c r="P61" s="13" t="inlineStr">
+      <c r="P61" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4900,7 +5036,7 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="10" t="inlineStr"/>
-      <c r="P62" s="13" t="inlineStr">
+      <c r="P62" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4965,7 +5101,7 @@
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="10" t="inlineStr"/>
-      <c r="P63" s="13" t="inlineStr">
+      <c r="P63" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5030,7 +5166,7 @@
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="10" t="inlineStr"/>
-      <c r="P64" s="13" t="inlineStr">
+      <c r="P64" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5050,12 +5186,12 @@
           <t>REF-062</t>
         </is>
       </c>
-      <c r="C65" s="17" t="inlineStr">
+      <c r="C65" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D65" s="17" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5095,7 +5231,7 @@
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="10" t="inlineStr"/>
-      <c r="P65" s="13" t="inlineStr">
+      <c r="P65" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5115,12 +5251,12 @@
           <t>REF-063</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C66" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5160,7 +5296,7 @@
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
       <c r="O66" s="10" t="inlineStr"/>
-      <c r="P66" s="13" t="inlineStr">
+      <c r="P66" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5180,12 +5316,12 @@
           <t>REF-064</t>
         </is>
       </c>
-      <c r="C67" s="17" t="inlineStr">
+      <c r="C67" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D67" s="17" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Géométrie vectorielle et filaire</t>
         </is>
@@ -5225,7 +5361,7 @@
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
-      <c r="P67" s="13" t="inlineStr">
+      <c r="P67" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5245,12 +5381,12 @@
           <t>REF-065</t>
         </is>
       </c>
-      <c r="C68" s="17" t="inlineStr">
+      <c r="C68" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Plan paramétrique</t>
         </is>
@@ -5290,12 +5426,16 @@
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="10" t="inlineStr"/>
-      <c r="P68" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q68" s="10" t="inlineStr"/>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q68" s="10" t="inlineStr">
+        <is>
+          <t>GP-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -5306,12 +5446,12 @@
           <t>REF-066</t>
         </is>
       </c>
-      <c r="C69" s="17" t="inlineStr">
+      <c r="C69" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D69" s="17" t="inlineStr">
+      <c r="D69" s="16" t="inlineStr">
         <is>
           <t>Plan paramétrique</t>
         </is>
@@ -5351,12 +5491,16 @@
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr"/>
-      <c r="P69" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q69" s="10" t="inlineStr"/>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q69" s="10" t="inlineStr">
+        <is>
+          <t>GP-01</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -5367,12 +5511,12 @@
           <t>REF-067</t>
         </is>
       </c>
-      <c r="C70" s="17" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Transformations et réseaux</t>
         </is>
@@ -5412,7 +5556,7 @@
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
       <c r="O70" s="10" t="inlineStr"/>
-      <c r="P70" s="13" t="inlineStr">
+      <c r="P70" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5432,12 +5576,12 @@
           <t>REF-068</t>
         </is>
       </c>
-      <c r="C71" s="17" t="inlineStr">
+      <c r="C71" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
+      <c r="D71" s="16" t="inlineStr">
         <is>
           <t>Transformations et réseaux</t>
         </is>
@@ -5477,7 +5621,7 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="13" t="inlineStr">
+      <c r="P71" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5497,12 +5641,12 @@
           <t>REF-069</t>
         </is>
       </c>
-      <c r="C72" s="17" t="inlineStr">
+      <c r="C72" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
+      <c r="D72" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -5542,7 +5686,7 @@
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="10" t="inlineStr"/>
-      <c r="P72" s="13" t="inlineStr">
+      <c r="P72" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5562,12 +5706,12 @@
           <t>REF-070</t>
         </is>
       </c>
-      <c r="C73" s="17" t="inlineStr">
+      <c r="C73" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D73" s="17" t="inlineStr">
+      <c r="D73" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -5607,7 +5751,7 @@
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="10" t="inlineStr"/>
-      <c r="P73" s="13" t="inlineStr">
+      <c r="P73" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5627,12 +5771,12 @@
           <t>REF-071</t>
         </is>
       </c>
-      <c r="C74" s="17" t="inlineStr">
+      <c r="C74" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D74" s="17" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -5672,7 +5816,7 @@
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr"/>
       <c r="O74" s="10" t="inlineStr"/>
-      <c r="P74" s="13" t="inlineStr">
+      <c r="P74" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5692,12 +5836,12 @@
           <t>REF-072</t>
         </is>
       </c>
-      <c r="C75" s="17" t="inlineStr">
+      <c r="C75" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D75" s="17" t="inlineStr">
+      <c r="D75" s="16" t="inlineStr">
         <is>
           <t>Surfaces et solides</t>
         </is>
@@ -5737,7 +5881,7 @@
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="10" t="inlineStr"/>
-      <c r="P75" s="13" t="inlineStr">
+      <c r="P75" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5757,12 +5901,12 @@
           <t>REF-073</t>
         </is>
       </c>
-      <c r="C76" s="17" t="inlineStr">
+      <c r="C76" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Synthèse géométrie</t>
         </is>
@@ -5802,12 +5946,16 @@
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
       <c r="O76" s="10" t="inlineStr"/>
-      <c r="P76" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q76" s="10" t="inlineStr"/>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q76" s="10" t="inlineStr">
+        <is>
+          <t>GP-02</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -5818,12 +5966,12 @@
           <t>REF-074</t>
         </is>
       </c>
-      <c r="C77" s="17" t="inlineStr">
+      <c r="C77" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D77" s="17" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -5863,12 +6011,16 @@
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
       <c r="O77" s="10" t="inlineStr"/>
-      <c r="P77" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q77" s="10" t="inlineStr"/>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q77" s="10" t="inlineStr">
+        <is>
+          <t>GP-03</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -5879,12 +6031,12 @@
           <t>REF-075</t>
         </is>
       </c>
-      <c r="C78" s="17" t="inlineStr">
+      <c r="C78" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D78" s="17" t="inlineStr">
+      <c r="D78" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -5924,12 +6076,16 @@
       <c r="M78" s="7" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
       <c r="O78" s="10" t="inlineStr"/>
-      <c r="P78" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q78" s="10" t="inlineStr"/>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q78" s="10" t="inlineStr">
+        <is>
+          <t>GP-03</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n">
@@ -5940,12 +6096,12 @@
           <t>REF-076</t>
         </is>
       </c>
-      <c r="C79" s="17" t="inlineStr">
+      <c r="C79" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D79" s="17" t="inlineStr">
+      <c r="D79" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -5985,12 +6141,16 @@
       <c r="M79" s="7" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
       <c r="O79" s="10" t="inlineStr"/>
-      <c r="P79" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q79" s="10" t="inlineStr"/>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q79" s="10" t="inlineStr">
+        <is>
+          <t>GP-03</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -6001,12 +6161,12 @@
           <t>REF-077</t>
         </is>
       </c>
-      <c r="C80" s="17" t="inlineStr">
+      <c r="C80" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D80" s="17" t="inlineStr">
+      <c r="D80" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6048,10 +6208,14 @@
       <c r="O80" s="10" t="inlineStr"/>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q80" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q80" s="10" t="inlineStr">
+        <is>
+          <t>GP-04</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n">
@@ -6062,12 +6226,12 @@
           <t>REF-078</t>
         </is>
       </c>
-      <c r="C81" s="17" t="inlineStr">
+      <c r="C81" s="16" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="D81" s="17" t="inlineStr">
+      <c r="D81" s="16" t="inlineStr">
         <is>
           <t>Maillages et SubD</t>
         </is>
@@ -6109,10 +6273,14 @@
       <c r="O81" s="10" t="inlineStr"/>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q81" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q81" s="10" t="inlineStr">
+        <is>
+          <t>GP-04</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n">
@@ -6123,12 +6291,12 @@
           <t>REF-079</t>
         </is>
       </c>
-      <c r="C82" s="18" t="inlineStr">
+      <c r="C82" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6168,7 +6336,7 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="10" t="inlineStr"/>
-      <c r="P82" s="13" t="inlineStr">
+      <c r="P82" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6188,12 +6356,12 @@
           <t>REF-080</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C83" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D83" s="18" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6233,7 +6401,7 @@
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr"/>
       <c r="O83" s="10" t="inlineStr"/>
-      <c r="P83" s="13" t="inlineStr">
+      <c r="P83" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6253,12 +6421,12 @@
           <t>REF-081</t>
         </is>
       </c>
-      <c r="C84" s="18" t="inlineStr">
+      <c r="C84" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D84" s="18" t="inlineStr">
+      <c r="D84" s="17" t="inlineStr">
         <is>
           <t>Mesures géométriques</t>
         </is>
@@ -6298,7 +6466,7 @@
       <c r="M84" s="7" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr"/>
       <c r="O84" s="10" t="inlineStr"/>
-      <c r="P84" s="13" t="inlineStr">
+      <c r="P84" s="12" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6318,12 +6486,12 @@
           <t>REF-082</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D85" s="18" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -6363,12 +6531,16 @@
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="10" t="inlineStr"/>
-      <c r="P85" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q85" s="10" t="inlineStr"/>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q85" s="10" t="inlineStr">
+        <is>
+          <t>QT-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -6379,12 +6551,12 @@
           <t>REF-083</t>
         </is>
       </c>
-      <c r="C86" s="18" t="inlineStr">
+      <c r="C86" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D86" s="18" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -6424,12 +6596,16 @@
       <c r="M86" s="7" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr"/>
       <c r="O86" s="10" t="inlineStr"/>
-      <c r="P86" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q86" s="10" t="inlineStr"/>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q86" s="10" t="inlineStr">
+        <is>
+          <t>QT-02</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n">
@@ -6440,12 +6616,12 @@
           <t>REF-084</t>
         </is>
       </c>
-      <c r="C87" s="18" t="inlineStr">
+      <c r="C87" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D87" s="18" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>Quantitatifs et chiffrage</t>
         </is>
@@ -6485,12 +6661,16 @@
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr"/>
       <c r="O87" s="10" t="inlineStr"/>
-      <c r="P87" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q87" s="10" t="inlineStr"/>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q87" s="10" t="inlineStr">
+        <is>
+          <t>QT-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n">
@@ -6501,12 +6681,12 @@
           <t>REF-085</t>
         </is>
       </c>
-      <c r="C88" s="18" t="inlineStr">
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D88" s="18" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -6546,12 +6726,16 @@
       <c r="M88" s="7" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
       <c r="O88" s="10" t="inlineStr"/>
-      <c r="P88" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q88" s="10" t="inlineStr"/>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q88" s="10" t="inlineStr">
+        <is>
+          <t>QT-03</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n">
@@ -6562,12 +6746,12 @@
           <t>REF-086</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
+      <c r="C89" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -6607,12 +6791,16 @@
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
       <c r="O89" s="10" t="inlineStr"/>
-      <c r="P89" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q89" s="10" t="inlineStr"/>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q89" s="10" t="inlineStr">
+        <is>
+          <t>QT-03</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -6623,12 +6811,12 @@
           <t>REF-087</t>
         </is>
       </c>
-      <c r="C90" s="18" t="inlineStr">
+      <c r="C90" s="17" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="D90" s="18" t="inlineStr">
+      <c r="D90" s="17" t="inlineStr">
         <is>
           <t>Export de données</t>
         </is>
@@ -6668,12 +6856,16 @@
       <c r="M90" s="7" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
       <c r="O90" s="10" t="inlineStr"/>
-      <c r="P90" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q90" s="10" t="inlineStr"/>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q90" s="10" t="inlineStr">
+        <is>
+          <t>QT-03</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n">
@@ -6684,12 +6876,12 @@
           <t>REF-088</t>
         </is>
       </c>
-      <c r="C91" s="19" t="inlineStr">
+      <c r="C91" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D91" s="18" t="inlineStr">
         <is>
           <t>Organisation et performance</t>
         </is>
@@ -6729,12 +6921,16 @@
       <c r="M91" s="7" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="10" t="inlineStr"/>
-      <c r="P91" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q91" s="10" t="inlineStr"/>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q91" s="10" t="inlineStr">
+        <is>
+          <t>MP-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -6745,12 +6941,12 @@
           <t>REF-089</t>
         </is>
       </c>
-      <c r="C92" s="19" t="inlineStr">
+      <c r="C92" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D92" s="19" t="inlineStr">
+      <c r="D92" s="18" t="inlineStr">
         <is>
           <t>Organisation et performance</t>
         </is>
@@ -6790,12 +6986,16 @@
       <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr"/>
       <c r="O92" s="10" t="inlineStr"/>
-      <c r="P92" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q92" s="10" t="inlineStr"/>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q92" s="10" t="inlineStr">
+        <is>
+          <t>MP-02</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n">
@@ -6806,12 +7006,12 @@
           <t>REF-090</t>
         </is>
       </c>
-      <c r="C93" s="19" t="inlineStr">
+      <c r="C93" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D93" s="19" t="inlineStr">
+      <c r="D93" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -6851,7 +7051,7 @@
       <c r="M93" s="7" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
       <c r="O93" s="10" t="inlineStr"/>
-      <c r="P93" s="15" t="inlineStr">
+      <c r="P93" s="11" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -6871,12 +7071,12 @@
           <t>REF-091</t>
         </is>
       </c>
-      <c r="C94" s="19" t="inlineStr">
+      <c r="C94" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D94" s="19" t="inlineStr">
+      <c r="D94" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -6918,10 +7118,14 @@
       <c r="O94" s="10" t="inlineStr"/>
       <c r="P94" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q94" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q94" s="10" t="inlineStr">
+        <is>
+          <t>MP-03</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -6932,12 +7136,12 @@
           <t>REF-092</t>
         </is>
       </c>
-      <c r="C95" s="19" t="inlineStr">
+      <c r="C95" s="18" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="D95" s="19" t="inlineStr">
+      <c r="D95" s="18" t="inlineStr">
         <is>
           <t>Chronologie et évènements</t>
         </is>
@@ -6979,10 +7183,14 @@
       <c r="O95" s="10" t="inlineStr"/>
       <c r="P95" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q95" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q95" s="10" t="inlineStr">
+        <is>
+          <t>MP-03</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n">
@@ -6993,12 +7201,12 @@
           <t>REF-093</t>
         </is>
       </c>
-      <c r="C96" s="20" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D96" s="20" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>Boucles et itération</t>
         </is>
@@ -7038,12 +7246,16 @@
       <c r="M96" s="7" t="inlineStr"/>
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="10" t="inlineStr"/>
-      <c r="P96" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q96" s="10" t="inlineStr"/>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q96" s="10" t="inlineStr">
+        <is>
+          <t>AV-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n">
@@ -7054,12 +7266,12 @@
           <t>REF-094</t>
         </is>
       </c>
-      <c r="C97" s="20" t="inlineStr">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D97" s="20" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Simulation physique</t>
         </is>
@@ -7099,12 +7311,16 @@
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="10" t="inlineStr"/>
-      <c r="P97" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q97" s="10" t="inlineStr"/>
+      <c r="P97" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q97" s="10" t="inlineStr">
+        <is>
+          <t>AV-02</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n">
@@ -7115,12 +7331,12 @@
           <t>REF-095</t>
         </is>
       </c>
-      <c r="C98" s="20" t="inlineStr">
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="D98" s="20" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>Design génératif</t>
         </is>
@@ -7160,12 +7376,16 @@
       <c r="M98" s="7" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
       <c r="O98" s="10" t="inlineStr"/>
-      <c r="P98" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q98" s="10" t="inlineStr"/>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q98" s="10" t="inlineStr">
+        <is>
+          <t>AV-03</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -7176,12 +7396,12 @@
           <t>REF-096</t>
         </is>
       </c>
-      <c r="C99" s="21" t="inlineStr">
+      <c r="C99" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D99" s="21" t="inlineStr">
+      <c r="D99" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -7221,12 +7441,16 @@
       <c r="M99" s="7" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="10" t="inlineStr"/>
-      <c r="P99" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q99" s="10" t="inlineStr"/>
+      <c r="P99" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q99" s="10" t="inlineStr">
+        <is>
+          <t>DV-04</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n">
@@ -7237,12 +7461,12 @@
           <t>REF-097</t>
         </is>
       </c>
-      <c r="C100" s="21" t="inlineStr">
+      <c r="C100" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D100" s="21" t="inlineStr">
+      <c r="D100" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -7282,12 +7506,16 @@
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="8" t="inlineStr"/>
       <c r="O100" s="10" t="inlineStr"/>
-      <c r="P100" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q100" s="10" t="inlineStr"/>
+      <c r="P100" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q100" s="10" t="inlineStr">
+        <is>
+          <t>DV-04</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n">
@@ -7298,12 +7526,12 @@
           <t>REF-098</t>
         </is>
       </c>
-      <c r="C101" s="21" t="inlineStr">
+      <c r="C101" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D101" s="21" t="inlineStr">
+      <c r="D101" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -7343,12 +7571,16 @@
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="8" t="inlineStr"/>
       <c r="O101" s="10" t="inlineStr"/>
-      <c r="P101" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q101" s="10" t="inlineStr"/>
+      <c r="P101" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q101" s="10" t="inlineStr">
+        <is>
+          <t>DV-04</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n">
@@ -7359,12 +7591,12 @@
           <t>REF-099</t>
         </is>
       </c>
-      <c r="C102" s="21" t="inlineStr">
+      <c r="C102" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D102" s="21" t="inlineStr">
+      <c r="D102" s="20" t="inlineStr">
         <is>
           <t>Compilation et IDE</t>
         </is>
@@ -7404,12 +7636,16 @@
       <c r="M102" s="7" t="inlineStr"/>
       <c r="N102" s="8" t="inlineStr"/>
       <c r="O102" s="10" t="inlineStr"/>
-      <c r="P102" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q102" s="10" t="inlineStr"/>
+      <c r="P102" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q102" s="10" t="inlineStr">
+        <is>
+          <t>DV-04</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -7420,12 +7656,12 @@
           <t>REF-100</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
+      <c r="C103" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D103" s="21" t="inlineStr">
+      <c r="D103" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -7467,10 +7703,14 @@
       <c r="O103" s="10" t="inlineStr"/>
       <c r="P103" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q103" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q103" s="10" t="inlineStr">
+        <is>
+          <t>DV-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n">
@@ -7481,12 +7721,12 @@
           <t>REF-101</t>
         </is>
       </c>
-      <c r="C104" s="21" t="inlineStr">
+      <c r="C104" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D104" s="21" t="inlineStr">
+      <c r="D104" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -7526,12 +7766,16 @@
       <c r="M104" s="7" t="inlineStr"/>
       <c r="N104" s="8" t="inlineStr"/>
       <c r="O104" s="10" t="inlineStr"/>
-      <c r="P104" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q104" s="10" t="inlineStr"/>
+      <c r="P104" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q104" s="10" t="inlineStr">
+        <is>
+          <t>DV-02</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n">
@@ -7542,12 +7786,12 @@
           <t>REF-102</t>
         </is>
       </c>
-      <c r="C105" s="21" t="inlineStr">
+      <c r="C105" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D105" s="21" t="inlineStr">
+      <c r="D105" s="20" t="inlineStr">
         <is>
           <t>Scripting dans Grasshopper</t>
         </is>
@@ -7587,12 +7831,16 @@
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
       <c r="O105" s="10" t="inlineStr"/>
-      <c r="P105" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q105" s="10" t="inlineStr"/>
+      <c r="P105" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q105" s="10" t="inlineStr">
+        <is>
+          <t>DV-02</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n">
@@ -7603,12 +7851,12 @@
           <t>REF-103</t>
         </is>
       </c>
-      <c r="C106" s="21" t="inlineStr">
+      <c r="C106" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D106" s="21" t="inlineStr">
+      <c r="D106" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -7648,12 +7896,16 @@
       <c r="M106" s="7" t="inlineStr"/>
       <c r="N106" s="8" t="inlineStr"/>
       <c r="O106" s="10" t="inlineStr"/>
-      <c r="P106" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q106" s="10" t="inlineStr"/>
+      <c r="P106" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q106" s="10" t="inlineStr">
+        <is>
+          <t>DV-02</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -7664,12 +7916,12 @@
           <t>REF-104</t>
         </is>
       </c>
-      <c r="C107" s="21" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D107" s="21" t="inlineStr">
+      <c r="D107" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -7711,10 +7963,14 @@
       <c r="O107" s="10" t="inlineStr"/>
       <c r="P107" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q107" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q107" s="10" t="inlineStr">
+        <is>
+          <t>DV-03</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -7725,12 +7981,12 @@
           <t>REF-105</t>
         </is>
       </c>
-      <c r="C108" s="21" t="inlineStr">
+      <c r="C108" s="20" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="D108" s="21" t="inlineStr">
+      <c r="D108" s="20" t="inlineStr">
         <is>
           <t>API et librairies</t>
         </is>
@@ -7772,10 +8028,14 @@
       <c r="O108" s="10" t="inlineStr"/>
       <c r="P108" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q108" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q108" s="10" t="inlineStr">
+        <is>
+          <t>DV-03</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -7786,12 +8046,12 @@
           <t>REF-106</t>
         </is>
       </c>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="C109" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
+      <c r="D109" s="21" t="inlineStr">
         <is>
           <t>Interfaces utilisateur</t>
         </is>
@@ -7831,12 +8091,16 @@
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="10" t="inlineStr"/>
-      <c r="P109" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q109" s="10" t="inlineStr"/>
+      <c r="P109" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q109" s="10" t="inlineStr">
+        <is>
+          <t>WB-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n">
@@ -7847,12 +8111,12 @@
           <t>REF-107</t>
         </is>
       </c>
-      <c r="C110" s="22" t="inlineStr">
+      <c r="C110" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D110" s="22" t="inlineStr">
+      <c r="D110" s="21" t="inlineStr">
         <is>
           <t>Interfaces utilisateur</t>
         </is>
@@ -7892,12 +8156,16 @@
       <c r="M110" s="7" t="inlineStr"/>
       <c r="N110" s="8" t="inlineStr"/>
       <c r="O110" s="10" t="inlineStr"/>
-      <c r="P110" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q110" s="10" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q110" s="10" t="inlineStr">
+        <is>
+          <t>WB-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -7908,12 +8176,12 @@
           <t>REF-108</t>
         </is>
       </c>
-      <c r="C111" s="22" t="inlineStr">
+      <c r="C111" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D111" s="22" t="inlineStr">
+      <c r="D111" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -7953,12 +8221,16 @@
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="10" t="inlineStr"/>
-      <c r="P111" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q111" s="10" t="inlineStr"/>
+      <c r="P111" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q111" s="10" t="inlineStr">
+        <is>
+          <t>WB-02</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -7969,12 +8241,12 @@
           <t>REF-109</t>
         </is>
       </c>
-      <c r="C112" s="22" t="inlineStr">
+      <c r="C112" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D112" s="22" t="inlineStr">
+      <c r="D112" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -8014,12 +8286,16 @@
       <c r="M112" s="7" t="inlineStr"/>
       <c r="N112" s="8" t="inlineStr"/>
       <c r="O112" s="10" t="inlineStr"/>
-      <c r="P112" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q112" s="10" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q112" s="10" t="inlineStr">
+        <is>
+          <t>WB-02</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -8030,12 +8306,12 @@
           <t>REF-110</t>
         </is>
       </c>
-      <c r="C113" s="22" t="inlineStr">
+      <c r="C113" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D113" s="22" t="inlineStr">
+      <c r="D113" s="21" t="inlineStr">
         <is>
           <t>Publication web</t>
         </is>
@@ -8075,12 +8351,16 @@
       <c r="M113" s="7" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
       <c r="O113" s="10" t="inlineStr"/>
-      <c r="P113" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q113" s="10" t="inlineStr"/>
+      <c r="P113" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q113" s="10" t="inlineStr">
+        <is>
+          <t>WB-02</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -8091,12 +8371,12 @@
           <t>REF-111</t>
         </is>
       </c>
-      <c r="C114" s="22" t="inlineStr">
+      <c r="C114" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D114" s="22" t="inlineStr">
+      <c r="D114" s="21" t="inlineStr">
         <is>
           <t>Interopérabilité</t>
         </is>
@@ -8138,10 +8418,14 @@
       <c r="O114" s="10" t="inlineStr"/>
       <c r="P114" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q114" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q114" s="10" t="inlineStr">
+        <is>
+          <t>WB-03</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n">
@@ -8152,12 +8436,12 @@
           <t>REF-112</t>
         </is>
       </c>
-      <c r="C115" s="22" t="inlineStr">
+      <c r="C115" s="21" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="D115" s="22" t="inlineStr">
+      <c r="D115" s="21" t="inlineStr">
         <is>
           <t>Interopérabilité</t>
         </is>
@@ -8199,10 +8483,14 @@
       <c r="O115" s="10" t="inlineStr"/>
       <c r="P115" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q115" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q115" s="10" t="inlineStr">
+        <is>
+          <t>WB-03</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n">
@@ -8213,12 +8501,12 @@
           <t>REF-113</t>
         </is>
       </c>
-      <c r="C116" s="23" t="inlineStr">
+      <c r="C116" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D116" s="23" t="inlineStr">
+      <c r="D116" s="22" t="inlineStr">
         <is>
           <t>Imbrication</t>
         </is>
@@ -8258,12 +8546,16 @@
       <c r="M116" s="7" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
       <c r="O116" s="10" t="inlineStr"/>
-      <c r="P116" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q116" s="10" t="inlineStr"/>
+      <c r="P116" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q116" s="10" t="inlineStr">
+        <is>
+          <t>FA-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n">
@@ -8274,12 +8566,12 @@
           <t>REF-114</t>
         </is>
       </c>
-      <c r="C117" s="23" t="inlineStr">
+      <c r="C117" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D117" s="23" t="inlineStr">
+      <c r="D117" s="22" t="inlineStr">
         <is>
           <t>Imbrication</t>
         </is>
@@ -8319,12 +8611,16 @@
       <c r="M117" s="7" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr"/>
       <c r="O117" s="10" t="inlineStr"/>
-      <c r="P117" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q117" s="10" t="inlineStr"/>
+      <c r="P117" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q117" s="10" t="inlineStr">
+        <is>
+          <t>FA-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n">
@@ -8335,12 +8631,12 @@
           <t>REF-115</t>
         </is>
       </c>
-      <c r="C118" s="23" t="inlineStr">
+      <c r="C118" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D118" s="23" t="inlineStr">
+      <c r="D118" s="22" t="inlineStr">
         <is>
           <t>Déroulé et mise à plat</t>
         </is>
@@ -8380,12 +8676,16 @@
       <c r="M118" s="7" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
       <c r="O118" s="10" t="inlineStr"/>
-      <c r="P118" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q118" s="10" t="inlineStr"/>
+      <c r="P118" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q118" s="10" t="inlineStr">
+        <is>
+          <t>FA-02</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n">
@@ -8396,12 +8696,12 @@
           <t>REF-116</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
+      <c r="C119" s="22" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="D119" s="23" t="inlineStr">
+      <c r="D119" s="22" t="inlineStr">
         <is>
           <t>Déroulé et mise à plat</t>
         </is>
@@ -8441,12 +8741,16 @@
       <c r="M119" s="7" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
       <c r="O119" s="10" t="inlineStr"/>
-      <c r="P119" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q119" s="10" t="inlineStr"/>
+      <c r="P119" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q119" s="10" t="inlineStr">
+        <is>
+          <t>FA-02</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n">
@@ -8457,12 +8761,12 @@
           <t>REF-117</t>
         </is>
       </c>
-      <c r="C120" s="24" t="inlineStr">
+      <c r="C120" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D120" s="24" t="inlineStr">
+      <c r="D120" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -8502,12 +8806,16 @@
       <c r="M120" s="7" t="inlineStr"/>
       <c r="N120" s="8" t="inlineStr"/>
       <c r="O120" s="10" t="inlineStr"/>
-      <c r="P120" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q120" s="10" t="inlineStr"/>
+      <c r="P120" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q120" s="10" t="inlineStr">
+        <is>
+          <t>IA-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n">
@@ -8518,12 +8826,12 @@
           <t>REF-118</t>
         </is>
       </c>
-      <c r="C121" s="24" t="inlineStr">
+      <c r="C121" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="D121" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -8565,10 +8873,14 @@
       <c r="O121" s="10" t="inlineStr"/>
       <c r="P121" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q121" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q121" s="10" t="inlineStr">
+        <is>
+          <t>IA-02</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n">
@@ -8579,12 +8891,12 @@
           <t>REF-119</t>
         </is>
       </c>
-      <c r="C122" s="24" t="inlineStr">
+      <c r="C122" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
+      <c r="D122" s="23" t="inlineStr">
         <is>
           <t>Formuler et cadrer une demande</t>
         </is>
@@ -8624,12 +8936,16 @@
       <c r="M122" s="7" t="inlineStr"/>
       <c r="N122" s="8" t="inlineStr"/>
       <c r="O122" s="10" t="inlineStr"/>
-      <c r="P122" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q122" s="10" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q122" s="10" t="inlineStr">
+        <is>
+          <t>IA-03</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
@@ -8640,12 +8956,12 @@
           <t>REF-120</t>
         </is>
       </c>
-      <c r="C123" s="24" t="inlineStr">
+      <c r="C123" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D123" s="24" t="inlineStr">
+      <c r="D123" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -8685,12 +9001,16 @@
       <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="8" t="inlineStr"/>
       <c r="O123" s="10" t="inlineStr"/>
-      <c r="P123" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q123" s="10" t="inlineStr"/>
+      <c r="P123" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q123" s="10" t="inlineStr">
+        <is>
+          <t>IA-04</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
@@ -8701,12 +9021,12 @@
           <t>REF-121</t>
         </is>
       </c>
-      <c r="C124" s="24" t="inlineStr">
+      <c r="C124" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D124" s="24" t="inlineStr">
+      <c r="D124" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -8746,12 +9066,16 @@
       <c r="M124" s="7" t="inlineStr"/>
       <c r="N124" s="8" t="inlineStr"/>
       <c r="O124" s="10" t="inlineStr"/>
-      <c r="P124" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q124" s="10" t="inlineStr"/>
+      <c r="P124" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q124" s="10" t="inlineStr">
+        <is>
+          <t>IA-04</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n">
@@ -8762,12 +9086,12 @@
           <t>REF-122</t>
         </is>
       </c>
-      <c r="C125" s="24" t="inlineStr">
+      <c r="C125" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D125" s="24" t="inlineStr">
+      <c r="D125" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -8807,12 +9131,16 @@
       <c r="M125" s="7" t="inlineStr"/>
       <c r="N125" s="8" t="inlineStr"/>
       <c r="O125" s="10" t="inlineStr"/>
-      <c r="P125" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q125" s="10" t="inlineStr"/>
+      <c r="P125" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q125" s="10" t="inlineStr">
+        <is>
+          <t>IA-06</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n">
@@ -8823,12 +9151,12 @@
           <t>REF-123</t>
         </is>
       </c>
-      <c r="C126" s="24" t="inlineStr">
+      <c r="C126" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D126" s="24" t="inlineStr">
+      <c r="D126" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -8868,12 +9196,16 @@
       <c r="M126" s="7" t="inlineStr"/>
       <c r="N126" s="8" t="inlineStr"/>
       <c r="O126" s="10" t="inlineStr"/>
-      <c r="P126" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q126" s="10" t="inlineStr"/>
+      <c r="P126" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q126" s="10" t="inlineStr">
+        <is>
+          <t>IA-06</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -8884,12 +9216,12 @@
           <t>REF-124</t>
         </is>
       </c>
-      <c r="C127" s="24" t="inlineStr">
+      <c r="C127" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D127" s="24" t="inlineStr">
+      <c r="D127" s="23" t="inlineStr">
         <is>
           <t>Composants scriptés assistés</t>
         </is>
@@ -8929,12 +9261,16 @@
       <c r="M127" s="7" t="inlineStr"/>
       <c r="N127" s="8" t="inlineStr"/>
       <c r="O127" s="10" t="inlineStr"/>
-      <c r="P127" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q127" s="10" t="inlineStr"/>
+      <c r="P127" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q127" s="10" t="inlineStr">
+        <is>
+          <t>IA-05</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -8945,12 +9281,12 @@
           <t>REF-125</t>
         </is>
       </c>
-      <c r="C128" s="24" t="inlineStr">
+      <c r="C128" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D128" s="24" t="inlineStr">
+      <c r="D128" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -8990,12 +9326,16 @@
       <c r="M128" s="7" t="inlineStr"/>
       <c r="N128" s="8" t="inlineStr"/>
       <c r="O128" s="10" t="inlineStr"/>
-      <c r="P128" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q128" s="10" t="inlineStr"/>
+      <c r="P128" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q128" s="10" t="inlineStr">
+        <is>
+          <t>IA-07</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n">
@@ -9006,12 +9346,12 @@
           <t>REF-126</t>
         </is>
       </c>
-      <c r="C129" s="24" t="inlineStr">
+      <c r="C129" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D129" s="24" t="inlineStr">
+      <c r="D129" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -9051,12 +9391,16 @@
       <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="8" t="inlineStr"/>
       <c r="O129" s="10" t="inlineStr"/>
-      <c r="P129" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q129" s="10" t="inlineStr"/>
+      <c r="P129" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q129" s="10" t="inlineStr">
+        <is>
+          <t>IA-07</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n">
@@ -9067,12 +9411,12 @@
           <t>REF-127</t>
         </is>
       </c>
-      <c r="C130" s="24" t="inlineStr">
+      <c r="C130" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D130" s="24" t="inlineStr">
+      <c r="D130" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -9112,12 +9456,16 @@
       <c r="M130" s="7" t="inlineStr"/>
       <c r="N130" s="8" t="inlineStr"/>
       <c r="O130" s="10" t="inlineStr"/>
-      <c r="P130" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q130" s="10" t="inlineStr"/>
+      <c r="P130" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q130" s="10" t="inlineStr">
+        <is>
+          <t>IA-07</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n">
@@ -9128,12 +9476,12 @@
           <t>REF-128</t>
         </is>
       </c>
-      <c r="C131" s="24" t="inlineStr">
+      <c r="C131" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D131" s="24" t="inlineStr">
+      <c r="D131" s="23" t="inlineStr">
         <is>
           <t>Développement de plugins assisté</t>
         </is>
@@ -9175,10 +9523,14 @@
       <c r="O131" s="10" t="inlineStr"/>
       <c r="P131" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q131" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q131" s="10" t="inlineStr">
+        <is>
+          <t>IA-08</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n">
@@ -9189,12 +9541,12 @@
           <t>REF-129</t>
         </is>
       </c>
-      <c r="C132" s="24" t="inlineStr">
+      <c r="C132" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D132" s="24" t="inlineStr">
+      <c r="D132" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -9234,12 +9586,16 @@
       <c r="M132" s="7" t="inlineStr"/>
       <c r="N132" s="8" t="inlineStr"/>
       <c r="O132" s="10" t="inlineStr"/>
-      <c r="P132" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q132" s="10" t="inlineStr"/>
+      <c r="P132" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q132" s="10" t="inlineStr">
+        <is>
+          <t>IA-09</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n">
@@ -9250,12 +9606,12 @@
           <t>REF-130</t>
         </is>
       </c>
-      <c r="C133" s="24" t="inlineStr">
+      <c r="C133" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D133" s="24" t="inlineStr">
+      <c r="D133" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -9295,12 +9651,16 @@
       <c r="M133" s="7" t="inlineStr"/>
       <c r="N133" s="8" t="inlineStr"/>
       <c r="O133" s="10" t="inlineStr"/>
-      <c r="P133" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q133" s="10" t="inlineStr"/>
+      <c r="P133" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q133" s="10" t="inlineStr">
+        <is>
+          <t>IA-10</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n">
@@ -9311,12 +9671,12 @@
           <t>REF-131</t>
         </is>
       </c>
-      <c r="C134" s="24" t="inlineStr">
+      <c r="C134" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D134" s="24" t="inlineStr">
+      <c r="D134" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -9356,12 +9716,16 @@
       <c r="M134" s="7" t="inlineStr"/>
       <c r="N134" s="8" t="inlineStr"/>
       <c r="O134" s="10" t="inlineStr"/>
-      <c r="P134" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q134" s="10" t="inlineStr"/>
+      <c r="P134" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q134" s="10" t="inlineStr">
+        <is>
+          <t>IA-09</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n">
@@ -9372,12 +9736,12 @@
           <t>REF-132</t>
         </is>
       </c>
-      <c r="C135" s="24" t="inlineStr">
+      <c r="C135" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D135" s="24" t="inlineStr">
+      <c r="D135" s="23" t="inlineStr">
         <is>
           <t>Apprentissage automatique</t>
         </is>
@@ -9417,12 +9781,16 @@
       <c r="M135" s="7" t="inlineStr"/>
       <c r="N135" s="8" t="inlineStr"/>
       <c r="O135" s="10" t="inlineStr"/>
-      <c r="P135" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q135" s="10" t="inlineStr"/>
+      <c r="P135" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q135" s="10" t="inlineStr">
+        <is>
+          <t>IA-09</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n">
@@ -9433,12 +9801,12 @@
           <t>REF-133</t>
         </is>
       </c>
-      <c r="C136" s="24" t="inlineStr">
+      <c r="C136" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D136" s="24" t="inlineStr">
+      <c r="D136" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -9478,12 +9846,16 @@
       <c r="M136" s="7" t="inlineStr"/>
       <c r="N136" s="8" t="inlineStr"/>
       <c r="O136" s="10" t="inlineStr"/>
-      <c r="P136" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q136" s="10" t="inlineStr"/>
+      <c r="P136" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q136" s="10" t="inlineStr">
+        <is>
+          <t>IA-11</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n">
@@ -9494,12 +9866,12 @@
           <t>REF-134</t>
         </is>
       </c>
-      <c r="C137" s="24" t="inlineStr">
+      <c r="C137" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D137" s="24" t="inlineStr">
+      <c r="D137" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -9539,12 +9911,16 @@
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="8" t="inlineStr"/>
       <c r="O137" s="10" t="inlineStr"/>
-      <c r="P137" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q137" s="10" t="inlineStr"/>
+      <c r="P137" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q137" s="10" t="inlineStr">
+        <is>
+          <t>IA-11</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n">
@@ -9555,12 +9931,12 @@
           <t>REF-135</t>
         </is>
       </c>
-      <c r="C138" s="24" t="inlineStr">
+      <c r="C138" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D138" s="24" t="inlineStr">
+      <c r="D138" s="23" t="inlineStr">
         <is>
           <t>Modèles de langage et IA générative</t>
         </is>
@@ -9600,12 +9976,16 @@
       <c r="M138" s="7" t="inlineStr"/>
       <c r="N138" s="8" t="inlineStr"/>
       <c r="O138" s="10" t="inlineStr"/>
-      <c r="P138" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q138" s="10" t="inlineStr"/>
+      <c r="P138" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q138" s="10" t="inlineStr">
+        <is>
+          <t>IA-11</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n">
@@ -9616,12 +9996,12 @@
           <t>REF-136</t>
         </is>
       </c>
-      <c r="C139" s="24" t="inlineStr">
+      <c r="C139" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D139" s="24" t="inlineStr">
+      <c r="D139" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -9661,12 +10041,16 @@
       <c r="M139" s="7" t="inlineStr"/>
       <c r="N139" s="8" t="inlineStr"/>
       <c r="O139" s="10" t="inlineStr"/>
-      <c r="P139" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q139" s="10" t="inlineStr"/>
+      <c r="P139" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q139" s="10" t="inlineStr">
+        <is>
+          <t>IA-12</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n">
@@ -9677,12 +10061,12 @@
           <t>REF-137</t>
         </is>
       </c>
-      <c r="C140" s="24" t="inlineStr">
+      <c r="C140" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D140" s="24" t="inlineStr">
+      <c r="D140" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -9722,12 +10106,16 @@
       <c r="M140" s="7" t="inlineStr"/>
       <c r="N140" s="8" t="inlineStr"/>
       <c r="O140" s="10" t="inlineStr"/>
-      <c r="P140" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q140" s="10" t="inlineStr"/>
+      <c r="P140" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q140" s="10" t="inlineStr">
+        <is>
+          <t>IA-12</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n">
@@ -9738,12 +10126,12 @@
           <t>REF-138</t>
         </is>
       </c>
-      <c r="C141" s="24" t="inlineStr">
+      <c r="C141" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D141" s="24" t="inlineStr">
+      <c r="D141" s="23" t="inlineStr">
         <is>
           <t>Agents et protocoles</t>
         </is>
@@ -9783,12 +10171,16 @@
       <c r="M141" s="7" t="inlineStr"/>
       <c r="N141" s="8" t="inlineStr"/>
       <c r="O141" s="10" t="inlineStr"/>
-      <c r="P141" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q141" s="10" t="inlineStr"/>
+      <c r="P141" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q141" s="10" t="inlineStr">
+        <is>
+          <t>IA-12</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n">
@@ -9799,12 +10191,12 @@
           <t>REF-139</t>
         </is>
       </c>
-      <c r="C142" s="24" t="inlineStr">
+      <c r="C142" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D142" s="24" t="inlineStr">
+      <c r="D142" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -9844,12 +10236,16 @@
       <c r="M142" s="7" t="inlineStr"/>
       <c r="N142" s="8" t="inlineStr"/>
       <c r="O142" s="10" t="inlineStr"/>
-      <c r="P142" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q142" s="10" t="inlineStr"/>
+      <c r="P142" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q142" s="10" t="inlineStr">
+        <is>
+          <t>IA-01, IA-14</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n">
@@ -9860,12 +10256,12 @@
           <t>REF-140</t>
         </is>
       </c>
-      <c r="C143" s="24" t="inlineStr">
+      <c r="C143" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D143" s="24" t="inlineStr">
+      <c r="D143" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -9907,10 +10303,14 @@
       <c r="O143" s="10" t="inlineStr"/>
       <c r="P143" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q143" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q143" s="10" t="inlineStr">
+        <is>
+          <t>IA-13</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n">
@@ -9921,12 +10321,12 @@
           <t>REF-141</t>
         </is>
       </c>
-      <c r="C144" s="24" t="inlineStr">
+      <c r="C144" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D144" s="24" t="inlineStr">
+      <c r="D144" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -9968,10 +10368,14 @@
       <c r="O144" s="10" t="inlineStr"/>
       <c r="P144" s="11" t="inlineStr">
         <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q144" s="10" t="inlineStr"/>
+          <t>Connaissance</t>
+        </is>
+      </c>
+      <c r="Q144" s="10" t="inlineStr">
+        <is>
+          <t>IA-13</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n">
@@ -9982,12 +10386,12 @@
           <t>REF-142</t>
         </is>
       </c>
-      <c r="C145" s="24" t="inlineStr">
+      <c r="C145" s="23" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="D145" s="24" t="inlineStr">
+      <c r="D145" s="23" t="inlineStr">
         <is>
           <t>Vérification, licences et limites</t>
         </is>
@@ -10027,12 +10431,16 @@
       <c r="M145" s="7" t="inlineStr"/>
       <c r="N145" s="8" t="inlineStr"/>
       <c r="O145" s="10" t="inlineStr"/>
-      <c r="P145" s="11" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="Q145" s="10" t="inlineStr"/>
+      <c r="P145" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
+        </is>
+      </c>
+      <c r="Q145" s="10" t="inlineStr">
+        <is>
+          <t>IA-14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:Q145"/>
@@ -21481,363 +21889,363 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Répartition par domaine</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Domaine</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>1 – Socle Rhino (prérequis)</t>
         </is>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>10 – Aide à la fabrication</t>
         </is>
       </c>
-      <c r="B6" s="28">
+      <c r="B6" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>11 – IA et assistance générative</t>
         </is>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>2 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="B8" s="28">
+      <c r="B8" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>3 – Données et logique</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>4 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>5 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>6 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>7 – Algorithmique avancée</t>
         </is>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>8 – Développement, scripting et API</t>
         </is>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>9 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <f>COUNTIF(Référentiel!$C$4:$C$145,$A$15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Répartition par niveau</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Niveau</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>Débutant</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$145,$A$19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Intermédiaire</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$145,$A$20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Perfectionnement</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$145,$A$21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Expert</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>COUNTIF(Référentiel!$G$4:$G$145,$A$22)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>Répartition par mode de validation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Mode de validation</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>ExactOrderedList</t>
         </is>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>SetEquality</t>
         </is>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>SingleValue</t>
         </is>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>NumericTolerance</t>
         </is>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>GeometryTolerance</t>
         </is>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Conceptuel (QCM)</t>
         </is>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <f>COUNTIF(Référentiel!$H$4:$H$145,$A$31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>Répartition par type d'exercice</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Type d'exercice</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>Nb notions</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Exercice Grasshopper</t>
         </is>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$145,$A$35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Exercice de synthèse</t>
         </is>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$145,$A$36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>QCM / question ciblée</t>
         </is>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$145,$A$37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>Démonstration formateur</t>
         </is>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <f>COUNTIF(Référentiel!$I$4:$I$145,$A$38)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Total des notions</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="28" t="n">
         <v>142</v>
       </c>
     </row>
@@ -21876,207 +22284,207 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Domaines</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Niveaux</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>ValidationMode</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Types d'exercice</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Priorités</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Statuts</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>0 – Socle Rhino (prérequis)</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Débutant</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>ExactOrderedList</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Exercice Grasshopper</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Pas commencé</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>1 – Environnement et principes Grasshopper</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Intermédiaire</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>SetEquality</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Exercice de synthèse</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>En cours</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>2 – Données et logique</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Perfectionnement</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>SingleValue</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>QCM / question ciblée</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>Terminé</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>3 – Géométrie paramétrique</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Expert</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>NumericTolerance</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Démonstration formateur</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>Bloqué</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>4 – Mesures, quantitatifs et export</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>GeometryTolerance</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>5 – Méthode, performance et évènements</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>Conceptuel (QCM)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>6 – Algorithmique avancée</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>7 – Développement, scripting et API</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>8 – Interfaces, web et interopérabilité</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>9 – Aide à la fabrication</t>
         </is>

--- a/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
@@ -5433,7 +5433,7 @@
       </c>
       <c r="Q68" s="10" t="inlineStr">
         <is>
-          <t>GP-01</t>
+          <t>GP-01, GP-05</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Q69" s="10" t="inlineStr">
         <is>
-          <t>GP-01</t>
+          <t>GP-01, GP-05</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Q88" s="10" t="inlineStr">
         <is>
-          <t>QT-03</t>
+          <t>QT-03, QT-04</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="Q89" s="10" t="inlineStr">
         <is>
-          <t>QT-03</t>
+          <t>QT-03, QT-05</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="Q90" s="10" t="inlineStr">
         <is>
-          <t>QT-03</t>
+          <t>QT-03, QT-05</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="Q99" s="10" t="inlineStr">
         <is>
-          <t>DV-04</t>
+          <t>DV-04, DV-05</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="Q100" s="10" t="inlineStr">
         <is>
-          <t>DV-04</t>
+          <t>DV-04, DV-06</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Q101" s="10" t="inlineStr">
         <is>
-          <t>DV-04</t>
+          <t>DV-04, DV-07</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="Q102" s="10" t="inlineStr">
         <is>
-          <t>DV-04</t>
+          <t>DV-04, DV-06</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
-          <t>WB-01</t>
+          <t>WB-01, WB-04</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
-          <t>WB-02</t>
+          <t>WB-02, WB-06</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="Q113" s="10" t="inlineStr">
         <is>
-          <t>WB-02</t>
+          <t>WB-02, WB-07</t>
         </is>
       </c>
     </row>
@@ -8481,14 +8481,14 @@
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="8" t="inlineStr"/>
       <c r="O115" s="10" t="inlineStr"/>
-      <c r="P115" s="11" t="inlineStr">
-        <is>
-          <t>Connaissance</t>
+      <c r="P115" s="12" t="inlineStr">
+        <is>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q115" s="10" t="inlineStr">
         <is>
-          <t>WB-03</t>
+          <t>WB-03, WB-05</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="Q117" s="10" t="inlineStr">
         <is>
-          <t>FA-01</t>
+          <t>FA-01, FA-04</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="Q119" s="10" t="inlineStr">
         <is>
-          <t>FA-02</t>
+          <t>FA-02, FA-03</t>
         </is>
       </c>
     </row>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="Q137" s="10" t="inlineStr">
         <is>
-          <t>IA-11</t>
+          <t>IA-11, IA-17</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
-          <t>IA-11</t>
+          <t>IA-11, IA-18</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="Q140" s="10" t="inlineStr">
         <is>
-          <t>IA-12</t>
+          <t>IA-12, IA-15</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="Q141" s="10" t="inlineStr">
         <is>
-          <t>IA-12</t>
+          <t>IA-12, IA-16</t>
         </is>
       </c>
     </row>

--- a/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
+++ b/Fondamentaux Grasshopper - IndB - 26-08-2026.xlsx
@@ -57,13 +57,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00B06A00"/>
+      <color rgb="001F7A3D"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F7A3D"/>
+      <color rgb="00B06A00"/>
       <sz val="10"/>
     </font>
     <font>
@@ -1264,12 +1264,12 @@
       <c r="O4" s="10" t="inlineStr"/>
       <c r="P4" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
-          <t>RH-01</t>
+          <t>RH-01, RH-11</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       <c r="O5" s="10" t="inlineStr"/>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q5" s="10" t="inlineStr">
         <is>
-          <t>RH-01</t>
+          <t>RH-01, RH-11, RH-12</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       <c r="O6" s="10" t="inlineStr"/>
       <c r="P6" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
-          <t>RH-01</t>
+          <t>RH-01, RH-11</t>
         </is>
       </c>
     </row>
@@ -1457,14 +1457,14 @@
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr"/>
       <c r="O7" s="10" t="inlineStr"/>
-      <c r="P7" s="12" t="inlineStr">
+      <c r="P7" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q7" s="10" t="inlineStr">
         <is>
-          <t>RH-02</t>
+          <t>RH-02, RH-13</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       <c r="M8" s="7" t="inlineStr"/>
       <c r="N8" s="8" t="inlineStr"/>
       <c r="O8" s="10" t="inlineStr"/>
-      <c r="P8" s="11" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -1587,14 +1587,14 @@
       <c r="M9" s="7" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr"/>
       <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="12" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q9" s="10" t="inlineStr">
         <is>
-          <t>RH-02</t>
+          <t>RH-02, RH-13</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       <c r="M10" s="7" t="inlineStr"/>
       <c r="N10" s="8" t="inlineStr"/>
       <c r="O10" s="10" t="inlineStr"/>
-      <c r="P10" s="12" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -1717,14 +1717,14 @@
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="8" t="inlineStr"/>
       <c r="O11" s="10" t="inlineStr"/>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q11" s="10" t="inlineStr">
         <is>
-          <t>RH-03</t>
+          <t>RH-03, RH-14</t>
         </is>
       </c>
     </row>
@@ -1782,14 +1782,14 @@
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="8" t="inlineStr"/>
       <c r="O12" s="10" t="inlineStr"/>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="P12" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>RH-04</t>
+          <t>RH-04, RH-15</t>
         </is>
       </c>
     </row>
@@ -1847,14 +1847,14 @@
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="8" t="inlineStr"/>
       <c r="O13" s="10" t="inlineStr"/>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>RH-04</t>
+          <t>RH-04, RH-16</t>
         </is>
       </c>
     </row>
@@ -1912,14 +1912,14 @@
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="8" t="inlineStr"/>
       <c r="O14" s="10" t="inlineStr"/>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="P14" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
-          <t>RH-04</t>
+          <t>RH-04, RH-16</t>
         </is>
       </c>
     </row>
@@ -1977,14 +1977,14 @@
       <c r="M15" s="7" t="inlineStr"/>
       <c r="N15" s="8" t="inlineStr"/>
       <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>RH-05</t>
+          <t>RH-05, RH-17</t>
         </is>
       </c>
     </row>
@@ -2042,14 +2042,14 @@
       <c r="M16" s="7" t="inlineStr"/>
       <c r="N16" s="8" t="inlineStr"/>
       <c r="O16" s="10" t="inlineStr"/>
-      <c r="P16" s="12" t="inlineStr">
+      <c r="P16" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>RH-03</t>
+          <t>RH-03, RH-14</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="8" t="inlineStr"/>
       <c r="O17" s="10" t="inlineStr"/>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="P17" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -2172,7 +2172,7 @@
       <c r="M18" s="7" t="inlineStr"/>
       <c r="N18" s="8" t="inlineStr"/>
       <c r="O18" s="10" t="inlineStr"/>
-      <c r="P18" s="11" t="inlineStr">
+      <c r="P18" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -2237,14 +2237,14 @@
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="8" t="inlineStr"/>
       <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="P19" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>RH-09</t>
+          <t>RH-09, RH-18</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       <c r="O20" s="10" t="inlineStr"/>
       <c r="P20" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q20" s="10" t="inlineStr">
         <is>
-          <t>RH-07</t>
+          <t>RH-07, RH-19</t>
         </is>
       </c>
     </row>
@@ -2367,14 +2367,14 @@
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="8" t="inlineStr"/>
       <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="P21" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>RH-09</t>
+          <t>RH-09, RH-19</t>
         </is>
       </c>
     </row>
@@ -2432,14 +2432,14 @@
       <c r="M22" s="7" t="inlineStr"/>
       <c r="N22" s="8" t="inlineStr"/>
       <c r="O22" s="10" t="inlineStr"/>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="P22" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>RH-08</t>
+          <t>RH-08, RH-20</t>
         </is>
       </c>
     </row>
@@ -2497,14 +2497,14 @@
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="8" t="inlineStr"/>
       <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="P23" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q23" s="10" t="inlineStr">
         <is>
-          <t>RH-08</t>
+          <t>RH-08, RH-20</t>
         </is>
       </c>
     </row>
@@ -2562,14 +2562,14 @@
       <c r="M24" s="7" t="inlineStr"/>
       <c r="N24" s="8" t="inlineStr"/>
       <c r="O24" s="10" t="inlineStr"/>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="P24" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
-          <t>RH-08</t>
+          <t>RH-08, RH-20</t>
         </is>
       </c>
     </row>
@@ -2627,14 +2627,14 @@
       <c r="M25" s="7" t="inlineStr"/>
       <c r="N25" s="8" t="inlineStr"/>
       <c r="O25" s="10" t="inlineStr"/>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="P25" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
         <is>
-          <t>RH-08</t>
+          <t>RH-08, RH-21</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2692,14 @@
       <c r="M26" s="7" t="inlineStr"/>
       <c r="N26" s="8" t="inlineStr"/>
       <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="P26" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
-          <t>RH-08</t>
+          <t>RH-08, RH-21</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       <c r="O27" s="10" t="inlineStr"/>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q27" s="10" t="inlineStr">
         <is>
-          <t>RH-10</t>
+          <t>RH-10, RH-22</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       <c r="M28" s="7" t="inlineStr"/>
       <c r="N28" s="8" t="inlineStr"/>
       <c r="O28" s="10" t="inlineStr"/>
-      <c r="P28" s="11" t="inlineStr">
+      <c r="P28" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -2887,7 +2887,7 @@
       <c r="M29" s="7" t="inlineStr"/>
       <c r="N29" s="8" t="inlineStr"/>
       <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="P29" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -2952,7 +2952,7 @@
       <c r="M30" s="7" t="inlineStr"/>
       <c r="N30" s="8" t="inlineStr"/>
       <c r="O30" s="10" t="inlineStr"/>
-      <c r="P30" s="12" t="inlineStr">
+      <c r="P30" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3017,7 +3017,7 @@
       <c r="M31" s="7" t="inlineStr"/>
       <c r="N31" s="8" t="inlineStr"/>
       <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="P31" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3084,12 +3084,12 @@
       <c r="O32" s="10" t="inlineStr"/>
       <c r="P32" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
         <is>
-          <t>PL-02</t>
+          <t>PL-02, PL-05, PL-10</t>
         </is>
       </c>
     </row>
@@ -3149,12 +3149,12 @@
       <c r="O33" s="10" t="inlineStr"/>
       <c r="P33" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q33" s="10" t="inlineStr">
         <is>
-          <t>PL-02</t>
+          <t>PL-02, PL-05, PL-09, PL-10</t>
         </is>
       </c>
     </row>
@@ -3212,14 +3212,14 @@
       <c r="M34" s="7" t="inlineStr"/>
       <c r="N34" s="8" t="inlineStr"/>
       <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="P34" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-08, PL-11</t>
         </is>
       </c>
     </row>
@@ -3277,14 +3277,14 @@
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="8" t="inlineStr"/>
       <c r="O35" s="10" t="inlineStr"/>
-      <c r="P35" s="12" t="inlineStr">
+      <c r="P35" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q35" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-08</t>
         </is>
       </c>
     </row>
@@ -3342,14 +3342,14 @@
       <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="8" t="inlineStr"/>
       <c r="O36" s="10" t="inlineStr"/>
-      <c r="P36" s="12" t="inlineStr">
+      <c r="P36" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-08</t>
         </is>
       </c>
     </row>
@@ -3407,14 +3407,14 @@
       <c r="M37" s="7" t="inlineStr"/>
       <c r="N37" s="8" t="inlineStr"/>
       <c r="O37" s="10" t="inlineStr"/>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="P37" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q37" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-11</t>
         </is>
       </c>
     </row>
@@ -3472,14 +3472,14 @@
       <c r="M38" s="7" t="inlineStr"/>
       <c r="N38" s="8" t="inlineStr"/>
       <c r="O38" s="10" t="inlineStr"/>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="P38" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-11</t>
         </is>
       </c>
     </row>
@@ -3537,14 +3537,14 @@
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="8" t="inlineStr"/>
       <c r="O39" s="10" t="inlineStr"/>
-      <c r="P39" s="12" t="inlineStr">
+      <c r="P39" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-11</t>
         </is>
       </c>
     </row>
@@ -3602,14 +3602,14 @@
       <c r="M40" s="7" t="inlineStr"/>
       <c r="N40" s="8" t="inlineStr"/>
       <c r="O40" s="10" t="inlineStr"/>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="P40" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>PL-03</t>
+          <t>PL-03, PL-11</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3669,12 @@
       <c r="O41" s="10" t="inlineStr"/>
       <c r="P41" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>PL-04</t>
+          <t>PL-04, PL-06, PL-07</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       <c r="O42" s="10" t="inlineStr"/>
       <c r="P42" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>PL-04</t>
+          <t>PL-04, PL-06, PL-07, PL-12</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
       <c r="O43" s="10" t="inlineStr"/>
-      <c r="P43" s="12" t="inlineStr">
+      <c r="P43" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3862,7 +3862,7 @@
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
       <c r="O44" s="10" t="inlineStr"/>
-      <c r="P44" s="11" t="inlineStr">
+      <c r="P44" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -3927,7 +3927,7 @@
       <c r="M45" s="7" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
       <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="12" t="inlineStr">
+      <c r="P45" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -3992,7 +3992,7 @@
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
       <c r="O46" s="10" t="inlineStr"/>
-      <c r="P46" s="12" t="inlineStr">
+      <c r="P46" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4057,7 +4057,7 @@
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="8" t="inlineStr"/>
       <c r="O47" s="10" t="inlineStr"/>
-      <c r="P47" s="12" t="inlineStr">
+      <c r="P47" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4122,7 +4122,7 @@
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
       <c r="O48" s="10" t="inlineStr"/>
-      <c r="P48" s="12" t="inlineStr">
+      <c r="P48" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4187,7 +4187,7 @@
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
       <c r="O49" s="10" t="inlineStr"/>
-      <c r="P49" s="12" t="inlineStr">
+      <c r="P49" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4252,7 +4252,7 @@
       <c r="M50" s="7" t="inlineStr"/>
       <c r="N50" s="8" t="inlineStr"/>
       <c r="O50" s="10" t="inlineStr"/>
-      <c r="P50" s="12" t="inlineStr">
+      <c r="P50" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4317,7 +4317,7 @@
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="8" t="inlineStr"/>
       <c r="O51" s="10" t="inlineStr"/>
-      <c r="P51" s="12" t="inlineStr">
+      <c r="P51" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4382,7 +4382,7 @@
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="8" t="inlineStr"/>
       <c r="O52" s="10" t="inlineStr"/>
-      <c r="P52" s="12" t="inlineStr">
+      <c r="P52" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4447,7 +4447,7 @@
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
       <c r="O53" s="10" t="inlineStr"/>
-      <c r="P53" s="12" t="inlineStr">
+      <c r="P53" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4512,7 +4512,7 @@
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="8" t="inlineStr"/>
       <c r="O54" s="10" t="inlineStr"/>
-      <c r="P54" s="12" t="inlineStr">
+      <c r="P54" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4577,7 +4577,7 @@
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
       <c r="O55" s="10" t="inlineStr"/>
-      <c r="P55" s="12" t="inlineStr">
+      <c r="P55" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4646,7 +4646,7 @@
           <t>⚠ Vérifié dans Rhino 8 le 26/08/2026 : la correspondance PAR DÉFAUT de Grasshopper n'est pas la troncature sur la liste la plus courte, mais la correspondance sur la liste la plus LONGUE, la liste courte étant prolongée par répétition de son dernier élément. Une liste de 10 et une liste de 4 dans une Addition produisent 10 résultats, pas 4. Le mode Shortest List existe mais doit être demandé explicitement par clic droit. L'intitulé de cette notion est donc à corriger.</t>
         </is>
       </c>
-      <c r="P56" s="11" t="inlineStr">
+      <c r="P56" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -4711,7 +4711,7 @@
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
       <c r="O57" s="10" t="inlineStr"/>
-      <c r="P57" s="12" t="inlineStr">
+      <c r="P57" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4776,7 +4776,7 @@
       <c r="M58" s="7" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
       <c r="O58" s="10" t="inlineStr"/>
-      <c r="P58" s="12" t="inlineStr">
+      <c r="P58" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4841,7 +4841,7 @@
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
       <c r="O59" s="10" t="inlineStr"/>
-      <c r="P59" s="11" t="inlineStr">
+      <c r="P59" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -4906,7 +4906,7 @@
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
       <c r="O60" s="10" t="inlineStr"/>
-      <c r="P60" s="12" t="inlineStr">
+      <c r="P60" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -4971,7 +4971,7 @@
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr"/>
       <c r="O61" s="10" t="inlineStr"/>
-      <c r="P61" s="12" t="inlineStr">
+      <c r="P61" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5036,7 +5036,7 @@
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
       <c r="O62" s="10" t="inlineStr"/>
-      <c r="P62" s="12" t="inlineStr">
+      <c r="P62" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5101,7 +5101,7 @@
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
       <c r="O63" s="10" t="inlineStr"/>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="P63" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5166,7 +5166,7 @@
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
       <c r="O64" s="10" t="inlineStr"/>
-      <c r="P64" s="12" t="inlineStr">
+      <c r="P64" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5231,7 +5231,7 @@
       <c r="M65" s="7" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="10" t="inlineStr"/>
-      <c r="P65" s="12" t="inlineStr">
+      <c r="P65" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5296,7 +5296,7 @@
       <c r="M66" s="7" t="inlineStr"/>
       <c r="N66" s="8" t="inlineStr"/>
       <c r="O66" s="10" t="inlineStr"/>
-      <c r="P66" s="12" t="inlineStr">
+      <c r="P66" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5361,7 +5361,7 @@
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="10" t="inlineStr"/>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="P67" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5426,7 +5426,7 @@
       <c r="M68" s="7" t="inlineStr"/>
       <c r="N68" s="8" t="inlineStr"/>
       <c r="O68" s="10" t="inlineStr"/>
-      <c r="P68" s="12" t="inlineStr">
+      <c r="P68" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5491,7 +5491,7 @@
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="8" t="inlineStr"/>
       <c r="O69" s="10" t="inlineStr"/>
-      <c r="P69" s="12" t="inlineStr">
+      <c r="P69" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5556,7 +5556,7 @@
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
       <c r="O70" s="10" t="inlineStr"/>
-      <c r="P70" s="12" t="inlineStr">
+      <c r="P70" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5621,7 +5621,7 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
       <c r="O71" s="10" t="inlineStr"/>
-      <c r="P71" s="12" t="inlineStr">
+      <c r="P71" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5686,7 +5686,7 @@
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr"/>
       <c r="O72" s="10" t="inlineStr"/>
-      <c r="P72" s="12" t="inlineStr">
+      <c r="P72" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5751,7 +5751,7 @@
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="8" t="inlineStr"/>
       <c r="O73" s="10" t="inlineStr"/>
-      <c r="P73" s="12" t="inlineStr">
+      <c r="P73" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5816,7 +5816,7 @@
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="8" t="inlineStr"/>
       <c r="O74" s="10" t="inlineStr"/>
-      <c r="P74" s="12" t="inlineStr">
+      <c r="P74" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5881,7 +5881,7 @@
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
       <c r="O75" s="10" t="inlineStr"/>
-      <c r="P75" s="12" t="inlineStr">
+      <c r="P75" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -5946,7 +5946,7 @@
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr"/>
       <c r="O76" s="10" t="inlineStr"/>
-      <c r="P76" s="12" t="inlineStr">
+      <c r="P76" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6011,14 +6011,14 @@
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
       <c r="O77" s="10" t="inlineStr"/>
-      <c r="P77" s="12" t="inlineStr">
+      <c r="P77" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q77" s="10" t="inlineStr">
         <is>
-          <t>GP-03</t>
+          <t>GP-03, GP-06</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       <c r="M78" s="7" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr"/>
       <c r="O78" s="10" t="inlineStr"/>
-      <c r="P78" s="12" t="inlineStr">
+      <c r="P78" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6141,14 +6141,14 @@
       <c r="M79" s="7" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr"/>
       <c r="O79" s="10" t="inlineStr"/>
-      <c r="P79" s="12" t="inlineStr">
+      <c r="P79" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>GP-03</t>
+          <t>GP-03, GP-07</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       <c r="O80" s="10" t="inlineStr"/>
       <c r="P80" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q80" s="10" t="inlineStr">
         <is>
-          <t>GP-04</t>
+          <t>GP-04, GP-08</t>
         </is>
       </c>
     </row>
@@ -6273,12 +6273,12 @@
       <c r="O81" s="10" t="inlineStr"/>
       <c r="P81" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q81" s="10" t="inlineStr">
         <is>
-          <t>GP-04</t>
+          <t>GP-04, GP-08</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr"/>
       <c r="O82" s="10" t="inlineStr"/>
-      <c r="P82" s="12" t="inlineStr">
+      <c r="P82" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6401,7 +6401,7 @@
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="8" t="inlineStr"/>
       <c r="O83" s="10" t="inlineStr"/>
-      <c r="P83" s="12" t="inlineStr">
+      <c r="P83" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6466,7 +6466,7 @@
       <c r="M84" s="7" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr"/>
       <c r="O84" s="10" t="inlineStr"/>
-      <c r="P84" s="12" t="inlineStr">
+      <c r="P84" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6531,7 +6531,7 @@
       <c r="M85" s="7" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="10" t="inlineStr"/>
-      <c r="P85" s="12" t="inlineStr">
+      <c r="P85" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6596,14 +6596,14 @@
       <c r="M86" s="7" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr"/>
       <c r="O86" s="10" t="inlineStr"/>
-      <c r="P86" s="12" t="inlineStr">
+      <c r="P86" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q86" s="10" t="inlineStr">
         <is>
-          <t>QT-02</t>
+          <t>QT-02, QT-06</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       <c r="M87" s="7" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr"/>
       <c r="O87" s="10" t="inlineStr"/>
-      <c r="P87" s="12" t="inlineStr">
+      <c r="P87" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6726,7 +6726,7 @@
       <c r="M88" s="7" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr"/>
       <c r="O88" s="10" t="inlineStr"/>
-      <c r="P88" s="12" t="inlineStr">
+      <c r="P88" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6791,7 +6791,7 @@
       <c r="M89" s="7" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr"/>
       <c r="O89" s="10" t="inlineStr"/>
-      <c r="P89" s="12" t="inlineStr">
+      <c r="P89" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6856,7 +6856,7 @@
       <c r="M90" s="7" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr"/>
       <c r="O90" s="10" t="inlineStr"/>
-      <c r="P90" s="12" t="inlineStr">
+      <c r="P90" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6921,7 +6921,7 @@
       <c r="M91" s="7" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="10" t="inlineStr"/>
-      <c r="P91" s="12" t="inlineStr">
+      <c r="P91" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -6986,7 +6986,7 @@
       <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr"/>
       <c r="O92" s="10" t="inlineStr"/>
-      <c r="P92" s="12" t="inlineStr">
+      <c r="P92" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7053,12 +7053,12 @@
       <c r="O93" s="10" t="inlineStr"/>
       <c r="P93" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q93" s="10" t="inlineStr">
         <is>
-          <t>A-26</t>
+          <t>A-26, MP-04</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7116,7 @@
       <c r="M94" s="7" t="inlineStr"/>
       <c r="N94" s="8" t="inlineStr"/>
       <c r="O94" s="10" t="inlineStr"/>
-      <c r="P94" s="11" t="inlineStr">
+      <c r="P94" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -7181,7 +7181,7 @@
       <c r="M95" s="7" t="inlineStr"/>
       <c r="N95" s="8" t="inlineStr"/>
       <c r="O95" s="10" t="inlineStr"/>
-      <c r="P95" s="11" t="inlineStr">
+      <c r="P95" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -7246,7 +7246,7 @@
       <c r="M96" s="7" t="inlineStr"/>
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="10" t="inlineStr"/>
-      <c r="P96" s="12" t="inlineStr">
+      <c r="P96" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7311,7 +7311,7 @@
       <c r="M97" s="7" t="inlineStr"/>
       <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="10" t="inlineStr"/>
-      <c r="P97" s="12" t="inlineStr">
+      <c r="P97" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7376,7 +7376,7 @@
       <c r="M98" s="7" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
       <c r="O98" s="10" t="inlineStr"/>
-      <c r="P98" s="12" t="inlineStr">
+      <c r="P98" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7441,7 +7441,7 @@
       <c r="M99" s="7" t="inlineStr"/>
       <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="10" t="inlineStr"/>
-      <c r="P99" s="12" t="inlineStr">
+      <c r="P99" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7506,7 +7506,7 @@
       <c r="M100" s="7" t="inlineStr"/>
       <c r="N100" s="8" t="inlineStr"/>
       <c r="O100" s="10" t="inlineStr"/>
-      <c r="P100" s="12" t="inlineStr">
+      <c r="P100" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7571,7 +7571,7 @@
       <c r="M101" s="7" t="inlineStr"/>
       <c r="N101" s="8" t="inlineStr"/>
       <c r="O101" s="10" t="inlineStr"/>
-      <c r="P101" s="12" t="inlineStr">
+      <c r="P101" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7636,7 +7636,7 @@
       <c r="M102" s="7" t="inlineStr"/>
       <c r="N102" s="8" t="inlineStr"/>
       <c r="O102" s="10" t="inlineStr"/>
-      <c r="P102" s="12" t="inlineStr">
+      <c r="P102" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7703,12 +7703,12 @@
       <c r="O103" s="10" t="inlineStr"/>
       <c r="P103" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q103" s="10" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-01, DV-09</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       <c r="M104" s="7" t="inlineStr"/>
       <c r="N104" s="8" t="inlineStr"/>
       <c r="O104" s="10" t="inlineStr"/>
-      <c r="P104" s="12" t="inlineStr">
+      <c r="P104" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7831,14 +7831,14 @@
       <c r="M105" s="7" t="inlineStr"/>
       <c r="N105" s="8" t="inlineStr"/>
       <c r="O105" s="10" t="inlineStr"/>
-      <c r="P105" s="12" t="inlineStr">
+      <c r="P105" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q105" s="10" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-02, DV-09</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       <c r="M106" s="7" t="inlineStr"/>
       <c r="N106" s="8" t="inlineStr"/>
       <c r="O106" s="10" t="inlineStr"/>
-      <c r="P106" s="12" t="inlineStr">
+      <c r="P106" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -7961,7 +7961,7 @@
       <c r="M107" s="7" t="inlineStr"/>
       <c r="N107" s="8" t="inlineStr"/>
       <c r="O107" s="10" t="inlineStr"/>
-      <c r="P107" s="11" t="inlineStr">
+      <c r="P107" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8028,12 +8028,12 @@
       <c r="O108" s="10" t="inlineStr"/>
       <c r="P108" s="11" t="inlineStr">
         <is>
-          <t>Connaissance</t>
+          <t>Compétence</t>
         </is>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
-          <t>DV-03</t>
+          <t>DV-03, DV-08</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       <c r="M109" s="7" t="inlineStr"/>
       <c r="N109" s="8" t="inlineStr"/>
       <c r="O109" s="10" t="inlineStr"/>
-      <c r="P109" s="12" t="inlineStr">
+      <c r="P109" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8156,7 +8156,7 @@
       <c r="M110" s="7" t="inlineStr"/>
       <c r="N110" s="8" t="inlineStr"/>
       <c r="O110" s="10" t="inlineStr"/>
-      <c r="P110" s="12" t="inlineStr">
+      <c r="P110" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8221,7 +8221,7 @@
       <c r="M111" s="7" t="inlineStr"/>
       <c r="N111" s="8" t="inlineStr"/>
       <c r="O111" s="10" t="inlineStr"/>
-      <c r="P111" s="12" t="inlineStr">
+      <c r="P111" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8286,7 +8286,7 @@
       <c r="M112" s="7" t="inlineStr"/>
       <c r="N112" s="8" t="inlineStr"/>
       <c r="O112" s="10" t="inlineStr"/>
-      <c r="P112" s="12" t="inlineStr">
+      <c r="P112" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8351,7 +8351,7 @@
       <c r="M113" s="7" t="inlineStr"/>
       <c r="N113" s="8" t="inlineStr"/>
       <c r="O113" s="10" t="inlineStr"/>
-      <c r="P113" s="12" t="inlineStr">
+      <c r="P113" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8416,7 +8416,7 @@
       <c r="M114" s="7" t="inlineStr"/>
       <c r="N114" s="8" t="inlineStr"/>
       <c r="O114" s="10" t="inlineStr"/>
-      <c r="P114" s="11" t="inlineStr">
+      <c r="P114" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8481,7 +8481,7 @@
       <c r="M115" s="7" t="inlineStr"/>
       <c r="N115" s="8" t="inlineStr"/>
       <c r="O115" s="10" t="inlineStr"/>
-      <c r="P115" s="12" t="inlineStr">
+      <c r="P115" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8546,7 +8546,7 @@
       <c r="M116" s="7" t="inlineStr"/>
       <c r="N116" s="8" t="inlineStr"/>
       <c r="O116" s="10" t="inlineStr"/>
-      <c r="P116" s="12" t="inlineStr">
+      <c r="P116" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8611,7 +8611,7 @@
       <c r="M117" s="7" t="inlineStr"/>
       <c r="N117" s="8" t="inlineStr"/>
       <c r="O117" s="10" t="inlineStr"/>
-      <c r="P117" s="12" t="inlineStr">
+      <c r="P117" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8676,7 +8676,7 @@
       <c r="M118" s="7" t="inlineStr"/>
       <c r="N118" s="8" t="inlineStr"/>
       <c r="O118" s="10" t="inlineStr"/>
-      <c r="P118" s="12" t="inlineStr">
+      <c r="P118" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8741,7 +8741,7 @@
       <c r="M119" s="7" t="inlineStr"/>
       <c r="N119" s="8" t="inlineStr"/>
       <c r="O119" s="10" t="inlineStr"/>
-      <c r="P119" s="12" t="inlineStr">
+      <c r="P119" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8806,7 +8806,7 @@
       <c r="M120" s="7" t="inlineStr"/>
       <c r="N120" s="8" t="inlineStr"/>
       <c r="O120" s="10" t="inlineStr"/>
-      <c r="P120" s="12" t="inlineStr">
+      <c r="P120" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -8871,7 +8871,7 @@
       <c r="M121" s="7" t="inlineStr"/>
       <c r="N121" s="8" t="inlineStr"/>
       <c r="O121" s="10" t="inlineStr"/>
-      <c r="P121" s="11" t="inlineStr">
+      <c r="P121" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -8936,7 +8936,7 @@
       <c r="M122" s="7" t="inlineStr"/>
       <c r="N122" s="8" t="inlineStr"/>
       <c r="O122" s="10" t="inlineStr"/>
-      <c r="P122" s="12" t="inlineStr">
+      <c r="P122" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9001,7 +9001,7 @@
       <c r="M123" s="7" t="inlineStr"/>
       <c r="N123" s="8" t="inlineStr"/>
       <c r="O123" s="10" t="inlineStr"/>
-      <c r="P123" s="12" t="inlineStr">
+      <c r="P123" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9066,14 +9066,14 @@
       <c r="M124" s="7" t="inlineStr"/>
       <c r="N124" s="8" t="inlineStr"/>
       <c r="O124" s="10" t="inlineStr"/>
-      <c r="P124" s="12" t="inlineStr">
+      <c r="P124" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q124" s="10" t="inlineStr">
         <is>
-          <t>IA-04</t>
+          <t>IA-04, IA-21</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9131,7 @@
       <c r="M125" s="7" t="inlineStr"/>
       <c r="N125" s="8" t="inlineStr"/>
       <c r="O125" s="10" t="inlineStr"/>
-      <c r="P125" s="12" t="inlineStr">
+      <c r="P125" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9196,14 +9196,14 @@
       <c r="M126" s="7" t="inlineStr"/>
       <c r="N126" s="8" t="inlineStr"/>
       <c r="O126" s="10" t="inlineStr"/>
-      <c r="P126" s="12" t="inlineStr">
+      <c r="P126" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
-          <t>IA-06</t>
+          <t>IA-06, IA-22</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       <c r="M127" s="7" t="inlineStr"/>
       <c r="N127" s="8" t="inlineStr"/>
       <c r="O127" s="10" t="inlineStr"/>
-      <c r="P127" s="12" t="inlineStr">
+      <c r="P127" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9326,7 +9326,7 @@
       <c r="M128" s="7" t="inlineStr"/>
       <c r="N128" s="8" t="inlineStr"/>
       <c r="O128" s="10" t="inlineStr"/>
-      <c r="P128" s="12" t="inlineStr">
+      <c r="P128" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9391,14 +9391,14 @@
       <c r="M129" s="7" t="inlineStr"/>
       <c r="N129" s="8" t="inlineStr"/>
       <c r="O129" s="10" t="inlineStr"/>
-      <c r="P129" s="12" t="inlineStr">
+      <c r="P129" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q129" s="10" t="inlineStr">
         <is>
-          <t>IA-07</t>
+          <t>IA-07, IA-23</t>
         </is>
       </c>
     </row>
@@ -9456,14 +9456,14 @@
       <c r="M130" s="7" t="inlineStr"/>
       <c r="N130" s="8" t="inlineStr"/>
       <c r="O130" s="10" t="inlineStr"/>
-      <c r="P130" s="12" t="inlineStr">
+      <c r="P130" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q130" s="10" t="inlineStr">
         <is>
-          <t>IA-07</t>
+          <t>IA-07, IA-24</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9521,7 @@
       <c r="M131" s="7" t="inlineStr"/>
       <c r="N131" s="8" t="inlineStr"/>
       <c r="O131" s="10" t="inlineStr"/>
-      <c r="P131" s="11" t="inlineStr">
+      <c r="P131" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -9586,7 +9586,7 @@
       <c r="M132" s="7" t="inlineStr"/>
       <c r="N132" s="8" t="inlineStr"/>
       <c r="O132" s="10" t="inlineStr"/>
-      <c r="P132" s="12" t="inlineStr">
+      <c r="P132" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9651,14 +9651,14 @@
       <c r="M133" s="7" t="inlineStr"/>
       <c r="N133" s="8" t="inlineStr"/>
       <c r="O133" s="10" t="inlineStr"/>
-      <c r="P133" s="12" t="inlineStr">
+      <c r="P133" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q133" s="10" t="inlineStr">
         <is>
-          <t>IA-10</t>
+          <t>IA-10, IA-19</t>
         </is>
       </c>
     </row>
@@ -9716,14 +9716,14 @@
       <c r="M134" s="7" t="inlineStr"/>
       <c r="N134" s="8" t="inlineStr"/>
       <c r="O134" s="10" t="inlineStr"/>
-      <c r="P134" s="12" t="inlineStr">
+      <c r="P134" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
-          <t>IA-09</t>
+          <t>IA-09, IA-20</t>
         </is>
       </c>
     </row>
@@ -9781,14 +9781,14 @@
       <c r="M135" s="7" t="inlineStr"/>
       <c r="N135" s="8" t="inlineStr"/>
       <c r="O135" s="10" t="inlineStr"/>
-      <c r="P135" s="12" t="inlineStr">
+      <c r="P135" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q135" s="10" t="inlineStr">
         <is>
-          <t>IA-09</t>
+          <t>IA-09, IA-20</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       <c r="M136" s="7" t="inlineStr"/>
       <c r="N136" s="8" t="inlineStr"/>
       <c r="O136" s="10" t="inlineStr"/>
-      <c r="P136" s="12" t="inlineStr">
+      <c r="P136" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9911,7 +9911,7 @@
       <c r="M137" s="7" t="inlineStr"/>
       <c r="N137" s="8" t="inlineStr"/>
       <c r="O137" s="10" t="inlineStr"/>
-      <c r="P137" s="12" t="inlineStr">
+      <c r="P137" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -9976,7 +9976,7 @@
       <c r="M138" s="7" t="inlineStr"/>
       <c r="N138" s="8" t="inlineStr"/>
       <c r="O138" s="10" t="inlineStr"/>
-      <c r="P138" s="12" t="inlineStr">
+      <c r="P138" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -10041,7 +10041,7 @@
       <c r="M139" s="7" t="inlineStr"/>
       <c r="N139" s="8" t="inlineStr"/>
       <c r="O139" s="10" t="inlineStr"/>
-      <c r="P139" s="12" t="inlineStr">
+      <c r="P139" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -10106,7 +10106,7 @@
       <c r="M140" s="7" t="inlineStr"/>
       <c r="N140" s="8" t="inlineStr"/>
       <c r="O140" s="10" t="inlineStr"/>
-      <c r="P140" s="12" t="inlineStr">
+      <c r="P140" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -10171,7 +10171,7 @@
       <c r="M141" s="7" t="inlineStr"/>
       <c r="N141" s="8" t="inlineStr"/>
       <c r="O141" s="10" t="inlineStr"/>
-      <c r="P141" s="12" t="inlineStr">
+      <c r="P141" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -10236,7 +10236,7 @@
       <c r="M142" s="7" t="inlineStr"/>
       <c r="N142" s="8" t="inlineStr"/>
       <c r="O142" s="10" t="inlineStr"/>
-      <c r="P142" s="12" t="inlineStr">
+      <c r="P142" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
@@ -10301,7 +10301,7 @@
       <c r="M143" s="7" t="inlineStr"/>
       <c r="N143" s="8" t="inlineStr"/>
       <c r="O143" s="10" t="inlineStr"/>
-      <c r="P143" s="11" t="inlineStr">
+      <c r="P143" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -10366,7 +10366,7 @@
       <c r="M144" s="7" t="inlineStr"/>
       <c r="N144" s="8" t="inlineStr"/>
       <c r="O144" s="10" t="inlineStr"/>
-      <c r="P144" s="11" t="inlineStr">
+      <c r="P144" s="12" t="inlineStr">
         <is>
           <t>Connaissance</t>
         </is>
@@ -10431,14 +10431,14 @@
       <c r="M145" s="7" t="inlineStr"/>
       <c r="N145" s="8" t="inlineStr"/>
       <c r="O145" s="10" t="inlineStr"/>
-      <c r="P145" s="12" t="inlineStr">
+      <c r="P145" s="11" t="inlineStr">
         <is>
           <t>Compétence</t>
         </is>
       </c>
       <c r="Q145" s="10" t="inlineStr">
         <is>
-          <t>IA-14</t>
+          <t>IA-14, IA-25</t>
         </is>
       </c>
     </row>
